--- a/2026/CABRERA/Junio/Junio CABRERA.xlsx
+++ b/2026/CABRERA/Junio/Junio CABRERA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137D91A-70EE-4D97-AC77-C5EDB43A699E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098F37F3-DC00-437E-8F76-69BB383360E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$95</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="135">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -381,9 +381,6 @@
     <t>Facundo Guarinello</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA - LIMPIEZA DE TANQUE</t>
-  </si>
-  <si>
     <t>Silvia Marin De Sarni</t>
   </si>
   <si>
@@ -399,40 +396,49 @@
     <t>Abdon alberto</t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Mes anterior - Se adeuda MAYO</t>
-  </si>
-  <si>
-    <t>Mes de ABRIL</t>
-  </si>
-  <si>
-    <t>Transf 04/05</t>
-  </si>
-  <si>
-    <t>Transf 06/05</t>
-  </si>
-  <si>
-    <t>Transf 08/05</t>
-  </si>
-  <si>
-    <t>Debito 05/05</t>
-  </si>
-  <si>
-    <t>Transf 11/05</t>
-  </si>
-  <si>
     <t>Ezequiel Mazzio</t>
   </si>
   <si>
-    <t>Transf 26/05</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saldo anterior </t>
   </si>
   <si>
-    <t>Hace unos meses venimos arrastrando una diferencia de caja de $51.266 (Tenemos mas en el banco de lo que dice el excel)- Revisar</t>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Mes anterior - Se adeuda JUNIO</t>
+  </si>
+  <si>
+    <t>Mes de MAYO</t>
+  </si>
+  <si>
+    <t>Debito 02/06</t>
+  </si>
+  <si>
+    <t>Gasto particular de arreglo porton</t>
+  </si>
+  <si>
+    <t>Transf 05/06</t>
+  </si>
+  <si>
+    <t>Transf 09/06</t>
+  </si>
+  <si>
+    <t>Transf 18/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascensores guillemi - Sumiistro y reemplazo de 6 patines de puerta en ascensor </t>
+  </si>
+  <si>
+    <t>Casa ruan materiales electricos</t>
+  </si>
+  <si>
+    <t>Aumentados en Jun10 a 108,000</t>
+  </si>
+  <si>
+    <t>Hace unos meses venimos arrastrando una diferencia de caja de $52.000 (Tenemos mas en el banco de lo que dice el excel)- Revisar</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,15 +577,6 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1040,7 +1037,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1054,7 +1051,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1074,8 +1070,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="17" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="16" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1093,14 +1088,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1111,22 +1106,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1143,7 +1138,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1153,13 +1147,12 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1175,8 +1168,8 @@
     <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1225,13 +1218,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1260,6 +1247,11 @@
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1367,9 +1359,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1759,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1774,65 +1763,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="77"/>
+      <c r="B1" s="75"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
     </row>
     <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="143"/>
-      <c r="B5" s="143"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
+      <c r="A5" s="140"/>
+      <c r="B5" s="140"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="143"/>
-      <c r="B6" s="143"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="A6" s="140"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
     </row>
     <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143"/>
-      <c r="B7" s="143"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
+      <c r="A7" s="140"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="151" t="s">
-        <v>121</v>
+      <c r="B9" s="148" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="151"/>
+      <c r="B10" s="148"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
+      <c r="B11" s="148"/>
     </row>
     <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
@@ -1846,30 +1835,30 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="144"/>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
+      <c r="B14" s="141"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="144"/>
-      <c r="B15" s="144"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="144"/>
+      <c r="A15" s="141"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="144"/>
-      <c r="D16" s="144"/>
+      <c r="A16" s="141"/>
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
-      <c r="B17" s="144"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="144"/>
+      <c r="A17" s="141"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1885,67 +1874,67 @@
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="92">
+      <c r="B23" s="51"/>
+      <c r="C23" s="88">
         <v>475000</v>
       </c>
-      <c r="D23" s="85" t="s">
-        <v>124</v>
+      <c r="D23" s="82" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="81"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="78"/>
     </row>
     <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="81"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="78"/>
     </row>
     <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="81"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="78"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="81"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="78"/>
     </row>
     <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="80"/>
-      <c r="C28" s="30">
+      <c r="B28" s="138"/>
+      <c r="C28" s="28">
         <f>SUM(C24:C27)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="54"/>
+      <c r="D28" s="52"/>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="55">
+      <c r="A29" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="53">
         <f>C23+C28</f>
         <v>475000</v>
       </c>
@@ -1953,555 +1942,588 @@
       <c r="F29" s="9"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="56"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="54"/>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="118" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="119"/>
-      <c r="C31" s="142">
+      <c r="A31" s="114" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="115"/>
+      <c r="C31" s="136">
         <v>102000</v>
       </c>
-      <c r="D31" s="90" t="s">
-        <v>128</v>
+      <c r="D31" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" t="s">
+        <v>132</v>
       </c>
       <c r="G31" s="9"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="55">
+      <c r="B32" s="13"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="53">
         <f>SUM(C31:C31)</f>
         <v>102000</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="37"/>
-    </row>
-    <row r="34" spans="1:6" s="22" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="149" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="150"/>
-      <c r="C34" s="112">
+      <c r="B33" s="13"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" s="21" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="146" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="147"/>
+      <c r="C34" s="108">
         <v>87769</v>
       </c>
-      <c r="D34" s="89" t="s">
-        <v>127</v>
+      <c r="D34" s="86" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="57">
+      <c r="B35" s="13"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="55">
         <f>SUM(C34:C34)</f>
         <v>87769</v>
       </c>
     </row>
     <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="121"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="58"/>
+      <c r="B36" s="116"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="56"/>
     </row>
     <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="113"/>
-      <c r="D37" s="89"/>
-      <c r="F37" s="83"/>
+      <c r="B37" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="109"/>
+      <c r="D37" s="86"/>
+      <c r="F37" s="80"/>
     </row>
     <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="94"/>
-      <c r="D38" s="89"/>
+      <c r="B38" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="90"/>
+      <c r="D38" s="86"/>
     </row>
     <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="89"/>
+      <c r="B39" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="90"/>
+      <c r="D39" s="86"/>
     </row>
     <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="88"/>
+      <c r="B40" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="90"/>
+      <c r="D40" s="85"/>
     </row>
     <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="121"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="57">
+      <c r="B41" s="116"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="55">
         <f>SUM(C37:C40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="121"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="58"/>
+      <c r="B42" s="116"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="56"/>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="53"/>
-      <c r="C43" s="94">
-        <v>96924.479999999996</v>
-      </c>
-      <c r="D43" s="87" t="s">
-        <v>125</v>
+      <c r="B43" s="51"/>
+      <c r="C43" s="90">
+        <v>96850.99</v>
+      </c>
+      <c r="D43" s="84" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
+      <c r="A44" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="53"/>
-      <c r="C44" s="94">
-        <v>205492.85</v>
-      </c>
-      <c r="D44" s="87" t="s">
-        <v>125</v>
+      <c r="B44" s="51"/>
+      <c r="C44" s="90">
+        <v>204648.47</v>
+      </c>
+      <c r="D44" s="84" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="94">
-        <v>324588.2</v>
-      </c>
-      <c r="D45" s="87" t="s">
-        <v>126</v>
+      <c r="B45" s="51"/>
+      <c r="C45" s="90">
+        <v>291150.46000000002</v>
+      </c>
+      <c r="D45" s="84" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="57">
+      <c r="B46" s="13"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="55">
         <f>SUM(C43:C45)</f>
-        <v>627005.53</v>
+        <v>592649.92000000004</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="60"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="58"/>
     </row>
     <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="149" t="s">
-        <v>118</v>
-      </c>
-      <c r="B48" s="150"/>
-      <c r="C48" s="94">
+      <c r="A48" s="146" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="147"/>
+      <c r="C48" s="90">
         <v>73200</v>
       </c>
-      <c r="D48" s="85" t="s">
+      <c r="D48" s="82" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="146" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="122"/>
-      <c r="B49" s="120"/>
-      <c r="C49" s="94"/>
-      <c r="D49" s="87"/>
-      <c r="E49" s="25"/>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="63">
-        <f>SUM(C48:C49)</f>
-        <v>73200</v>
-      </c>
+      <c r="B49" s="147"/>
+      <c r="C49" s="90">
+        <v>120915</v>
+      </c>
+      <c r="D49" s="82"/>
+    </row>
+    <row r="50" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="146" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="147"/>
+      <c r="C50" s="90">
+        <v>28000</v>
+      </c>
+      <c r="D50" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="24"/>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="61">
+        <f>SUM(C48:C50)</f>
+        <v>222115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="123"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="60"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="53" t="s">
+      <c r="B52" s="117"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="58"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B52" s="53"/>
-      <c r="C52" s="94">
+      <c r="B53" s="51"/>
+      <c r="C53" s="90">
         <v>69000</v>
       </c>
-      <c r="D52" s="64"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="53" t="s">
+      <c r="D53" s="62"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="53"/>
-      <c r="C53" s="94">
-        <v>37109.67</v>
-      </c>
-      <c r="D53" s="62"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="124" t="s">
+      <c r="B54" s="51"/>
+      <c r="C54" s="90">
+        <v>42788.86</v>
+      </c>
+      <c r="D54" s="60"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="124"/>
-      <c r="C54" s="65"/>
-      <c r="D54" s="57">
-        <f>SUM(C52:C53)</f>
-        <v>106109.67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="53"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="66"/>
-    </row>
-    <row r="56" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="145" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="146"/>
-      <c r="C56" s="147"/>
-      <c r="D56" s="67"/>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="125"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="69"/>
-      <c r="E57" s="25"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="55">
+        <f>SUM(C53:C54)</f>
+        <v>111788.86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="51"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="51"/>
+      <c r="D56" s="64"/>
+    </row>
+    <row r="57" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="142" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="143"/>
+      <c r="C57" s="144"/>
+      <c r="D57" s="65">
+        <f>1700000-1591322.78</f>
+        <v>108677.21999999997</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="126" t="s">
+      <c r="A58" s="119"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="24"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="127"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="71">
-        <f>(SUM(D24:D56))</f>
-        <v>1471084.2</v>
-      </c>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="68"/>
-      <c r="B59" s="68"/>
+      <c r="B59" s="121"/>
       <c r="C59" s="68"/>
-      <c r="D59" s="68"/>
-      <c r="F59" s="84"/>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="68"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="68"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="128" t="s">
+      <c r="D59" s="69">
+        <f>(SUM(D24:D57))</f>
+        <v>1700000</v>
+      </c>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="66"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="F60" s="81"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="66"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="66"/>
+      <c r="D61" s="66"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="129"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="73"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="149"/>
-      <c r="B62" s="150"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="59"/>
+      <c r="B62" s="123"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="71"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="149"/>
-      <c r="B63" s="150"/>
-      <c r="C63" s="61"/>
-      <c r="D63" s="59"/>
+      <c r="A63" s="146"/>
+      <c r="B63" s="147"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="57"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="130"/>
-      <c r="B64" s="131"/>
-      <c r="C64" s="61"/>
-      <c r="D64" s="59"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="132"/>
-      <c r="B65" s="133"/>
-      <c r="C65" s="134"/>
-      <c r="D65" s="31">
-        <f>SUM(C62:C64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="68"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-    </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="68"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="135" t="s">
+      <c r="A64" s="146"/>
+      <c r="B64" s="147"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="57"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="124"/>
+      <c r="B65" s="125"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="57"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="126"/>
+      <c r="B66" s="127"/>
+      <c r="C66" s="128"/>
+      <c r="D66" s="29">
+        <f>SUM(C63:C65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="66"/>
+      <c r="B67" s="66"/>
+      <c r="C67" s="66"/>
+    </row>
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="66"/>
+      <c r="B68" s="66"/>
+      <c r="C68" s="66"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="B68" s="135"/>
-      <c r="C68" s="136"/>
-      <c r="D68" s="91"/>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="68"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="126" t="s">
+      <c r="B69" s="129"/>
+      <c r="C69" s="130"/>
+      <c r="D69" s="87"/>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="66"/>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B70" s="127"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="38">
-        <f>D65+D68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="68"/>
-      <c r="B71" s="68"/>
+      <c r="B71" s="121"/>
       <c r="C71" s="68"/>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="137" t="s">
+      <c r="D71" s="36">
+        <f>D66+D69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="66"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="B72" s="138">
-        <f>D58</f>
-        <v>1471084.2</v>
-      </c>
-      <c r="C72" s="139"/>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="137" t="s">
+      <c r="B73" s="132">
+        <f>D59</f>
+        <v>1700000</v>
+      </c>
+      <c r="C73" s="133"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B73" s="138">
-        <f>D58-D56</f>
-        <v>1471084.2</v>
-      </c>
-      <c r="C73" s="68"/>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="137" t="s">
+      <c r="B74" s="132">
+        <f>D59-D57</f>
+        <v>1591322.78</v>
+      </c>
+      <c r="C74" s="66"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="B74" s="138">
-        <f>D70-D68</f>
-        <v>0</v>
-      </c>
-      <c r="C74" s="68"/>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="137" t="s">
+      <c r="B75" s="132">
+        <f>D71-D69</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="66"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="138">
-        <f>D70</f>
-        <v>0</v>
-      </c>
-      <c r="C75" s="68"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="68"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="68"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="68"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="68"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="68"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="68"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="140" t="s">
+      <c r="B76" s="132">
+        <f>D71</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="66"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="66"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="66"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="66"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="66"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="66"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B79" s="141"/>
-      <c r="C79" s="68"/>
-    </row>
-    <row r="80" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="106" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="76">
-        <v>733575.9600000002</v>
-      </c>
-      <c r="C80" s="139"/>
-      <c r="D80" s="25"/>
-      <c r="G80" s="179" t="s">
-        <v>132</v>
-      </c>
+      <c r="B80" s="135"/>
+      <c r="C80" s="66"/>
     </row>
     <row r="81" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="107" t="s">
+      <c r="A81" s="102" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="74">
+        <v>483066.42000000039</v>
+      </c>
+      <c r="C81" s="133"/>
+      <c r="D81" s="24"/>
+      <c r="G81" s="139" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="22">
         <f>PRORRATEO!G18</f>
-        <v>1220574.6600000001</v>
-      </c>
-      <c r="G81" s="179"/>
-    </row>
-    <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="107" t="s">
+        <v>1394145.56</v>
+      </c>
+      <c r="G82" s="139"/>
+    </row>
+    <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="B82" s="62">
-        <f>B92</f>
-        <v>0</v>
-      </c>
-      <c r="G82" s="179"/>
-    </row>
-    <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="10" t="s">
+      <c r="B83" s="60">
+        <f>B94</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="139"/>
+    </row>
+    <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="103" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="83">
+        <v>-45000</v>
+      </c>
+      <c r="G84" s="139"/>
+    </row>
+    <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B83" s="86">
-        <f>-B73</f>
-        <v>-1471084.2</v>
-      </c>
-      <c r="G83" s="179"/>
-    </row>
-    <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="10" t="s">
+      <c r="B85" s="83">
+        <f>-B74</f>
+        <v>-1591322.78</v>
+      </c>
+      <c r="G85" s="139"/>
+    </row>
+    <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B84" s="62">
-        <f>-(B74)</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="179"/>
-    </row>
-    <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="108" t="s">
+      <c r="B86" s="60">
+        <f>-(B75)</f>
+        <v>0</v>
+      </c>
+      <c r="G86" s="139"/>
+    </row>
+    <row r="87" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="B85" s="76">
-        <f>SUM(B80:B84)</f>
-        <v>483066.42000000039</v>
-      </c>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25"/>
-      <c r="G85" s="179"/>
-    </row>
-    <row r="86" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="24"/>
-      <c r="C86" s="25"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="148" t="s">
+      <c r="B87" s="74">
+        <f>SUM(B81:B86)</f>
+        <v>240889.20000000042</v>
+      </c>
+      <c r="C87" s="24"/>
+      <c r="D87" s="24"/>
+      <c r="G87" s="139"/>
+    </row>
+    <row r="88" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="23"/>
+      <c r="C88" s="24"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="B88" s="148"/>
-    </row>
-    <row r="89" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="148"/>
-      <c r="B89" s="148"/>
-    </row>
-    <row r="90" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="74"/>
-      <c r="B90" s="18"/>
-    </row>
-    <row r="91" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="74"/>
-      <c r="B91" s="18"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="26" t="s">
+      <c r="B90" s="145"/>
+    </row>
+    <row r="91" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="145"/>
+      <c r="B91" s="145"/>
+    </row>
+    <row r="92" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="72"/>
+      <c r="B92" s="17"/>
+    </row>
+    <row r="93" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="72"/>
+      <c r="B93" s="17"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B92" s="75">
-        <f>SUM(B90:B91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L93" s="4"/>
+      <c r="B94" s="73">
+        <f>SUM(B92:B93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L95" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="G80:G85"/>
+  <mergeCells count="12">
+    <mergeCell ref="G81:G87"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A88:B89"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A90:B91"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A62:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2536,527 +2558,527 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-      <c r="B1" s="156" t="str">
+      <c r="B1" s="153" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="156" t="s">
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="153" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="152" t="s">
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="149" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="153"/>
-      <c r="L1" s="114" t="s">
+      <c r="K1" s="150"/>
+      <c r="L1" s="110" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="114"/>
-      <c r="N1" s="116">
-        <f>1250000+(1250000*15%)</f>
-        <v>1437500</v>
-      </c>
-      <c r="O1" s="109"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="112">
+        <v>1700000</v>
+      </c>
+      <c r="O1" s="105"/>
       <c r="P1" s="9"/>
     </row>
     <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="154"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="115" t="s">
+      <c r="B2" s="156"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="111" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="115"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="110"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="106"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="162" t="s">
+      <c r="A3" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="161" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="166" t="s">
+      <c r="C3" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="166" t="s">
+      <c r="D3" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="166" t="s">
+      <c r="F3" s="163" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="163" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="166" t="s">
+      <c r="H3" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="174" t="s">
+      <c r="I3" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="172" t="s">
+      <c r="J3" s="169" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="172" t="s">
+      <c r="K3" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="172" t="s">
+      <c r="L3" s="169" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="177" t="s">
+      <c r="M3" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="34" t="s">
+      <c r="N3" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="168" t="s">
+      <c r="O3" s="165" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="25"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="163"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="171"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="171"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="32" t="str">
+      <c r="A4" s="160"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="168"/>
+      <c r="I4" s="172"/>
+      <c r="J4" s="170"/>
+      <c r="K4" s="173"/>
+      <c r="L4" s="170"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="30" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="O4" s="169"/>
+        <v>VTO 17/07</v>
+      </c>
+      <c r="O4" s="166"/>
     </row>
     <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="34">
         <v>6.84</v>
       </c>
-      <c r="F5" s="40">
-        <v>82935.009999999995</v>
-      </c>
-      <c r="G5" s="41">
-        <v>85423</v>
-      </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="43">
+      <c r="F5" s="38">
+        <v>95837.01</v>
+      </c>
+      <c r="G5" s="39">
+        <v>98712</v>
+      </c>
+      <c r="H5" s="40"/>
+      <c r="I5" s="41">
         <f>F5-G5</f>
-        <v>-2487.9900000000052</v>
-      </c>
-      <c r="J5" s="43">
+        <v>-2874.9900000000052</v>
+      </c>
+      <c r="J5" s="41">
         <f>IF(I5&gt;0,I5*2.95%,0)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="42">
         <f t="shared" ref="K5:K16" si="0">N$2*E5%</f>
         <v>0</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="42">
         <f t="shared" ref="L5:L16" si="1">N$1*E5%</f>
-        <v>98325</v>
-      </c>
-      <c r="M5" s="45">
-        <v>0</v>
-      </c>
-      <c r="N5" s="46">
+        <v>116280</v>
+      </c>
+      <c r="M5" s="43">
+        <v>0</v>
+      </c>
+      <c r="N5" s="44">
         <f>ROUND(I5+J5+K5+L5+M5,0) + P5</f>
-        <v>95837.01</v>
-      </c>
-      <c r="O5" s="47">
+        <v>113405.01</v>
+      </c>
+      <c r="O5" s="45">
         <f t="shared" ref="O5:O16" si="2">ROUND(N5*3%,0) + N5</f>
-        <v>98712.01</v>
-      </c>
-      <c r="P5" s="25">
+        <v>116807.01</v>
+      </c>
+      <c r="P5" s="24">
         <v>0.01</v>
       </c>
-      <c r="Q5" s="25" t="s">
-        <v>119</v>
+      <c r="Q5" s="24" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="C6" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="D6" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="100">
         <v>7.79</v>
       </c>
-      <c r="F6" s="40">
-        <v>91230.02</v>
-      </c>
-      <c r="G6" s="41">
+      <c r="F6" s="38">
+        <v>115340.02</v>
+      </c>
+      <c r="G6" s="39">
         <f>F6</f>
-        <v>91230.02</v>
-      </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="97">
+        <v>115340.02</v>
+      </c>
+      <c r="H6" s="40"/>
+      <c r="I6" s="93">
         <f t="shared" ref="I6:I16" si="3">F6-G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="97">
+      <c r="J6" s="93">
         <f t="shared" ref="J6:J16" si="4">IF(I6&gt;0,I6*2.95%,0)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="98">
+      <c r="K6" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="98">
+      <c r="L6" s="94">
         <f t="shared" si="1"/>
-        <v>111981.25</v>
-      </c>
-      <c r="M6" s="99">
-        <v>0</v>
-      </c>
-      <c r="N6" s="100">
+        <v>132430</v>
+      </c>
+      <c r="M6" s="95">
+        <v>0</v>
+      </c>
+      <c r="N6" s="96">
         <f t="shared" ref="N6:N16" si="5">ROUND(SUM(I6:M6),0) + P6</f>
-        <v>111981.02</v>
-      </c>
-      <c r="O6" s="101">
+        <v>132430.01999999999</v>
+      </c>
+      <c r="O6" s="97">
         <f t="shared" si="2"/>
-        <v>115340.02</v>
-      </c>
-      <c r="P6" s="25">
+        <v>136403.01999999999</v>
+      </c>
+      <c r="P6" s="24">
         <f>P5+0.01</f>
         <v>0.02</v>
       </c>
       <c r="Q6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="117" t="s">
+      <c r="A7" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="C7" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="103" t="s">
+      <c r="D7" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="104">
+      <c r="E7" s="100">
         <v>6.75</v>
       </c>
-      <c r="F7" s="41">
-        <v>84375.03</v>
-      </c>
-      <c r="G7" s="41">
+      <c r="F7" s="39">
+        <v>97031.03</v>
+      </c>
+      <c r="G7" s="39">
         <f>F7</f>
-        <v>84375.03</v>
-      </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="43">
+        <v>97031.03</v>
+      </c>
+      <c r="H7" s="40"/>
+      <c r="I7" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="42">
         <f t="shared" si="1"/>
-        <v>97031.25</v>
-      </c>
-      <c r="M7" s="45">
-        <v>0</v>
-      </c>
-      <c r="N7" s="46">
+        <v>114750.00000000001</v>
+      </c>
+      <c r="M7" s="43">
+        <v>0</v>
+      </c>
+      <c r="N7" s="44">
         <f t="shared" si="5"/>
-        <v>97031.03</v>
-      </c>
-      <c r="O7" s="47">
+        <v>114750.03</v>
+      </c>
+      <c r="O7" s="45">
         <f t="shared" si="2"/>
-        <v>99942.03</v>
-      </c>
-      <c r="P7" s="25">
+        <v>118193.03</v>
+      </c>
+      <c r="P7" s="24">
         <f t="shared" ref="P7:P16" si="6">P6+0.01</f>
         <v>0.03</v>
       </c>
       <c r="Q7" t="s">
-        <v>129</v>
-      </c>
-      <c r="R7" s="25"/>
+        <v>120</v>
+      </c>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="100">
         <v>7.41</v>
       </c>
-      <c r="F8" s="41">
-        <v>92625.04</v>
-      </c>
-      <c r="G8" s="41">
+      <c r="F8" s="39">
+        <v>106519.03999999999</v>
+      </c>
+      <c r="G8" s="39">
         <f>F8</f>
-        <v>92625.04</v>
-      </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="43">
+        <v>106519.03999999999</v>
+      </c>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="42">
         <f t="shared" si="1"/>
-        <v>106518.75</v>
-      </c>
-      <c r="M8" s="45">
-        <v>0</v>
-      </c>
-      <c r="N8" s="46">
+        <v>125970</v>
+      </c>
+      <c r="M8" s="43">
+        <v>0</v>
+      </c>
+      <c r="N8" s="44">
         <f t="shared" si="5"/>
-        <v>106519.03999999999</v>
-      </c>
-      <c r="O8" s="47">
+        <v>125970.04</v>
+      </c>
+      <c r="O8" s="45">
         <f t="shared" si="2"/>
-        <v>109715.04</v>
-      </c>
-      <c r="P8" s="25">
+        <v>129749.04</v>
+      </c>
+      <c r="P8" s="24">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="Q8" t="s">
         <v>113</v>
       </c>
-      <c r="R8" s="25"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="D9" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="111">
+      <c r="E9" s="107">
         <v>8</v>
       </c>
-      <c r="F9" s="40">
-        <v>100000.05</v>
-      </c>
-      <c r="G9" s="41">
-        <v>101000</v>
-      </c>
-      <c r="H9" s="42"/>
-      <c r="I9" s="43">
+      <c r="F9" s="38">
+        <v>114000.05</v>
+      </c>
+      <c r="G9" s="39">
+        <v>115000</v>
+      </c>
+      <c r="H9" s="40"/>
+      <c r="I9" s="41">
         <f t="shared" si="3"/>
         <v>-999.94999999999709</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="44">
+      <c r="L9" s="42">
         <f t="shared" si="1"/>
-        <v>115000</v>
-      </c>
-      <c r="M9" s="45">
-        <v>0</v>
-      </c>
-      <c r="N9" s="46">
+        <v>136000</v>
+      </c>
+      <c r="M9" s="43">
+        <v>45000</v>
+      </c>
+      <c r="N9" s="44">
         <f t="shared" si="5"/>
-        <v>114000.05</v>
-      </c>
-      <c r="O9" s="47">
+        <v>180000.05</v>
+      </c>
+      <c r="O9" s="45">
         <f t="shared" si="2"/>
-        <v>117420.05</v>
-      </c>
-      <c r="P9" s="25">
+        <v>185400.05</v>
+      </c>
+      <c r="P9" s="24">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
       <c r="Q9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="103" t="s">
+      <c r="D10" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="102">
+      <c r="E10" s="98">
         <v>6.97</v>
       </c>
-      <c r="F10" s="40">
-        <v>141665.06</v>
-      </c>
-      <c r="G10" s="41">
-        <v>90000</v>
-      </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="43">
+      <c r="F10" s="38">
+        <v>153383.06</v>
+      </c>
+      <c r="G10" s="39">
+        <f>50000+50000+50000</f>
+        <v>150000</v>
+      </c>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41">
         <f t="shared" si="3"/>
-        <v>51665.06</v>
-      </c>
-      <c r="J10" s="43">
+        <v>3383.0599999999977</v>
+      </c>
+      <c r="J10" s="41">
         <f t="shared" si="4"/>
-        <v>1524.1192700000001</v>
-      </c>
-      <c r="K10" s="44">
+        <v>99.800269999999941</v>
+      </c>
+      <c r="K10" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="44">
+      <c r="L10" s="42">
         <f t="shared" si="1"/>
-        <v>100193.75</v>
-      </c>
-      <c r="M10" s="45">
-        <v>0</v>
-      </c>
-      <c r="N10" s="46">
+        <v>118490</v>
+      </c>
+      <c r="M10" s="43">
+        <v>0</v>
+      </c>
+      <c r="N10" s="44">
         <f t="shared" si="5"/>
-        <v>153383.06</v>
-      </c>
-      <c r="O10" s="47">
+        <v>121973.06</v>
+      </c>
+      <c r="O10" s="45">
         <f t="shared" si="2"/>
-        <v>157984.06</v>
-      </c>
-      <c r="P10" s="25">
+        <v>125632.06</v>
+      </c>
+      <c r="P10" s="24">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="Q10" s="84"/>
-      <c r="R10" s="83"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="80"/>
     </row>
     <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="98" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="105">
+      <c r="E11" s="101">
         <v>6.75</v>
       </c>
-      <c r="F11" s="40">
-        <v>84375.07</v>
-      </c>
-      <c r="G11" s="41">
+      <c r="F11" s="38">
+        <v>97031.07</v>
+      </c>
+      <c r="G11" s="39">
         <f>F11</f>
-        <v>84375.07</v>
-      </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="43">
+        <v>97031.07</v>
+      </c>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="42">
         <f t="shared" si="1"/>
-        <v>97031.25</v>
-      </c>
-      <c r="M11" s="45">
-        <v>0</v>
-      </c>
-      <c r="N11" s="46">
+        <v>114750.00000000001</v>
+      </c>
+      <c r="M11" s="43">
+        <v>0</v>
+      </c>
+      <c r="N11" s="44">
         <f t="shared" si="5"/>
-        <v>97031.07</v>
-      </c>
-      <c r="O11" s="47">
+        <v>114750.07</v>
+      </c>
+      <c r="O11" s="45">
         <f t="shared" si="2"/>
-        <v>99942.07</v>
-      </c>
-      <c r="P11" s="25">
+        <v>118193.07</v>
+      </c>
+      <c r="P11" s="24">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
@@ -3068,54 +3090,54 @@
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="98" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="98" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="102" t="s">
+      <c r="D12" s="98" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="105">
+      <c r="E12" s="101">
         <v>7.79</v>
       </c>
-      <c r="F12" s="40">
-        <v>97375.08</v>
-      </c>
-      <c r="G12" s="41">
+      <c r="F12" s="38">
+        <v>111981.08</v>
+      </c>
+      <c r="G12" s="39">
         <f>F12</f>
-        <v>97375.08</v>
-      </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="43">
+        <v>111981.08</v>
+      </c>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J12" s="43">
+      <c r="J12" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="42">
         <f t="shared" si="1"/>
-        <v>111981.25</v>
-      </c>
-      <c r="M12" s="45">
-        <v>0</v>
-      </c>
-      <c r="N12" s="46">
+        <v>132430</v>
+      </c>
+      <c r="M12" s="43">
+        <v>0</v>
+      </c>
+      <c r="N12" s="44">
         <f t="shared" si="5"/>
-        <v>111981.08</v>
-      </c>
-      <c r="O12" s="47">
+        <v>132430.07999999999</v>
+      </c>
+      <c r="O12" s="45">
         <f t="shared" si="2"/>
-        <v>115340.08</v>
-      </c>
-      <c r="P12" s="25">
+        <v>136403.07999999999</v>
+      </c>
+      <c r="P12" s="24">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
@@ -3124,54 +3146,54 @@
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="103" t="s">
+      <c r="D13" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="104">
+      <c r="E13" s="100">
         <v>7.62</v>
       </c>
-      <c r="F13" s="41">
-        <v>95250.09</v>
-      </c>
-      <c r="G13" s="41">
+      <c r="F13" s="39">
+        <v>112824.09</v>
+      </c>
+      <c r="G13" s="39">
         <f>F13</f>
-        <v>95250.09</v>
-      </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43">
+        <v>112824.09</v>
+      </c>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J13" s="43">
+      <c r="J13" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="42">
         <f t="shared" si="1"/>
-        <v>109537.5</v>
-      </c>
-      <c r="M13" s="45">
-        <v>0</v>
-      </c>
-      <c r="N13" s="46">
+        <v>129540</v>
+      </c>
+      <c r="M13" s="43">
+        <v>0</v>
+      </c>
+      <c r="N13" s="44">
         <f t="shared" si="5"/>
-        <v>109538.09</v>
-      </c>
-      <c r="O13" s="47">
+        <v>129540.09</v>
+      </c>
+      <c r="O13" s="45">
         <f t="shared" si="2"/>
-        <v>112824.09</v>
-      </c>
-      <c r="P13" s="25">
+        <v>133426.09</v>
+      </c>
+      <c r="P13" s="24">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
@@ -3183,54 +3205,53 @@
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="102" t="s">
+      <c r="C14" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="102" t="s">
+      <c r="D14" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="105">
+      <c r="E14" s="101">
         <v>6.97</v>
       </c>
-      <c r="F14" s="40">
-        <v>87046.1</v>
-      </c>
-      <c r="G14" s="41">
-        <f>60000+27046.1</f>
-        <v>87046.1</v>
-      </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="43">
+      <c r="F14" s="38">
+        <v>100194.1</v>
+      </c>
+      <c r="G14" s="39">
+        <v>0</v>
+      </c>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="43">
+        <v>100194.1</v>
+      </c>
+      <c r="J14" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="44">
+        <v>2955.7259500000005</v>
+      </c>
+      <c r="K14" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="44">
+      <c r="L14" s="42">
         <f t="shared" si="1"/>
-        <v>100193.75</v>
-      </c>
-      <c r="M14" s="45">
-        <v>0</v>
-      </c>
-      <c r="N14" s="46">
+        <v>118490</v>
+      </c>
+      <c r="M14" s="43">
+        <v>0</v>
+      </c>
+      <c r="N14" s="44">
         <f t="shared" si="5"/>
-        <v>100194.1</v>
-      </c>
-      <c r="O14" s="47">
+        <v>221640.1</v>
+      </c>
+      <c r="O14" s="45">
         <f t="shared" si="2"/>
-        <v>103200.1</v>
-      </c>
-      <c r="P14" s="25">
+        <v>228289.1</v>
+      </c>
+      <c r="P14" s="24">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
@@ -3239,54 +3260,54 @@
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="102" t="s">
+      <c r="C15" s="98" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="D15" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="105">
+      <c r="E15" s="101">
         <v>14.01</v>
       </c>
-      <c r="F15" s="40">
-        <v>148125.10999999999</v>
-      </c>
-      <c r="G15" s="41">
+      <c r="F15" s="38">
+        <v>201394.11</v>
+      </c>
+      <c r="G15" s="39">
         <f>F15</f>
-        <v>148125.10999999999</v>
-      </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43">
+        <v>201394.11</v>
+      </c>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="42">
         <f t="shared" si="1"/>
-        <v>201393.75</v>
-      </c>
-      <c r="M15" s="45">
-        <v>0</v>
-      </c>
-      <c r="N15" s="46">
+        <v>238170</v>
+      </c>
+      <c r="M15" s="43">
+        <v>0</v>
+      </c>
+      <c r="N15" s="44">
         <f t="shared" si="5"/>
-        <v>201394.11</v>
-      </c>
-      <c r="O15" s="47">
+        <v>238170.11</v>
+      </c>
+      <c r="O15" s="45">
         <f t="shared" si="2"/>
-        <v>207436.11</v>
-      </c>
-      <c r="P15" s="25">
+        <v>245315.11</v>
+      </c>
+      <c r="P15" s="24">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
@@ -3298,54 +3319,54 @@
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="98" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="102" t="s">
+      <c r="C16" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="105">
+      <c r="E16" s="101">
         <v>13.1</v>
       </c>
-      <c r="F16" s="40">
-        <v>163750.12</v>
-      </c>
-      <c r="G16" s="41">
+      <c r="F16" s="38">
+        <v>188313.12</v>
+      </c>
+      <c r="G16" s="39">
         <f>F16</f>
-        <v>163750.12</v>
-      </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43">
+        <v>188313.12</v>
+      </c>
+      <c r="H16" s="40"/>
+      <c r="I16" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K16" s="44">
+      <c r="K16" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="44">
+      <c r="L16" s="42">
         <f t="shared" si="1"/>
-        <v>188312.5</v>
-      </c>
-      <c r="M16" s="45">
-        <v>0</v>
-      </c>
-      <c r="N16" s="46">
+        <v>222700</v>
+      </c>
+      <c r="M16" s="43">
+        <v>0</v>
+      </c>
+      <c r="N16" s="44">
         <f t="shared" si="5"/>
-        <v>188313.12</v>
-      </c>
-      <c r="O16" s="47">
+        <v>222700.12</v>
+      </c>
+      <c r="O16" s="45">
         <f t="shared" si="2"/>
-        <v>193962.12</v>
-      </c>
-      <c r="P16" s="25">
+        <v>229381.12</v>
+      </c>
+      <c r="P16" s="24">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
@@ -3357,147 +3378,147 @@
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="25"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="24"/>
     </row>
     <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="51">
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="49">
         <f>SUM(E5:E17)</f>
         <v>100</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="27">
         <f>SUM(F5:F17)</f>
-        <v>1268751.7799999998</v>
-      </c>
-      <c r="G18" s="33">
+        <v>1493847.7800000003</v>
+      </c>
+      <c r="G18" s="31">
         <f>SUM(G5:G17)</f>
-        <v>1220574.6600000001</v>
-      </c>
-      <c r="H18" s="33">
+        <v>1394145.56</v>
+      </c>
+      <c r="H18" s="31">
         <f>SUM(H5:H17)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33">
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31">
         <f>SUM(K5:K17)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="33">
+      <c r="L18" s="31">
         <f>SUM(L5:L17)</f>
-        <v>1437500</v>
-      </c>
-      <c r="M18" s="33">
+        <v>1700000</v>
+      </c>
+      <c r="M18" s="31">
         <f>SUM(M5:M17)</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="52">
+        <v>45000</v>
+      </c>
+      <c r="N18" s="50">
         <f>SUM(N5:N17)</f>
-        <v>1487202.7800000003</v>
-      </c>
-      <c r="O18" s="52">
+        <v>1847758.7800000003</v>
+      </c>
+      <c r="O18" s="50">
         <f>SUM(O5:O17)</f>
-        <v>1531817.7800000003</v>
+        <v>1903191.7800000003</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D19" s="27"/>
+      <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D20" s="170" t="s">
+      <c r="D20" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="170"/>
-      <c r="K20" s="170"/>
-      <c r="L20" s="170"/>
-      <c r="M20" s="170"/>
-      <c r="N20" s="170"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="167"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D21" s="170"/>
-      <c r="E21" s="170"/>
-      <c r="F21" s="170"/>
-      <c r="G21" s="170"/>
-      <c r="H21" s="170"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="170"/>
-      <c r="K21" s="170"/>
-      <c r="L21" s="170"/>
-      <c r="M21" s="170"/>
-      <c r="N21" s="170"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="167"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
+      <c r="J21" s="167"/>
+      <c r="K21" s="167"/>
+      <c r="L21" s="167"/>
+      <c r="M21" s="167"/>
+      <c r="N21" s="167"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D22" s="170"/>
-      <c r="E22" s="170"/>
-      <c r="F22" s="170"/>
-      <c r="G22" s="170"/>
-      <c r="H22" s="170"/>
-      <c r="I22" s="170"/>
-      <c r="J22" s="170"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="170"/>
-      <c r="M22" s="170"/>
-      <c r="N22" s="170"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="167"/>
+      <c r="G22" s="167"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
+      <c r="J22" s="167"/>
+      <c r="K22" s="167"/>
+      <c r="L22" s="167"/>
+      <c r="M22" s="167"/>
+      <c r="N22" s="167"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D23" s="170"/>
-      <c r="E23" s="170"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="170"/>
-      <c r="I23" s="170"/>
-      <c r="J23" s="170"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="170"/>
-      <c r="M23" s="170"/>
-      <c r="N23" s="170"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="167"/>
+      <c r="H23" s="167"/>
+      <c r="I23" s="167"/>
+      <c r="J23" s="167"/>
+      <c r="K23" s="167"/>
+      <c r="L23" s="167"/>
+      <c r="M23" s="167"/>
+      <c r="N23" s="167"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D24" s="170"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="170"/>
-      <c r="H24" s="170"/>
-      <c r="I24" s="170"/>
-      <c r="J24" s="170"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="170"/>
-      <c r="M24" s="170"/>
-      <c r="N24" s="170"/>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="167"/>
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="167"/>
+      <c r="N24" s="167"/>
     </row>
     <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="170"/>
-      <c r="E25" s="170"/>
-      <c r="F25" s="170"/>
-      <c r="G25" s="170"/>
-      <c r="H25" s="170"/>
-      <c r="I25" s="170"/>
-      <c r="J25" s="170"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="170"/>
-      <c r="M25" s="170"/>
-      <c r="N25" s="170"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="167"/>
+      <c r="G25" s="167"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="167"/>
+      <c r="J25" s="167"/>
+      <c r="K25" s="167"/>
+      <c r="L25" s="167"/>
+      <c r="M25" s="167"/>
+      <c r="N25" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3531,7 +3552,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C4" s="83"/>
+      <c r="C4" s="80"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
